--- a/04-northbridge-cloudworks-grc-program/01-enterprise-risk-assessment/artifacts/Northbridge-Enterprise-Risk-Assessment.xlsx
+++ b/04-northbridge-cloudworks-grc-program/01-enterprise-risk-assessment/artifacts/Northbridge-Enterprise-Risk-Assessment.xlsx
@@ -13,9 +13,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$1:$H$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Methodology'!$A$1:$G$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Risk Register'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Risk Register'!$A$1:$X$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Risk Register'!$A$1:$Y$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Treatment Plan'!$A$1:$H$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'References'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'References'!$A$1:$C$19</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -1028,193 +1028,173 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>R-001</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>Identity and Access Management</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="inlineStr">
-        <is>
-          <t>Okta / Microsoft 365 / AWS Admin</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="E12" s="30" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F12" s="30" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="G12" s="30" t="inlineStr">
-        <is>
-          <t>VP of IT</t>
-        </is>
-      </c>
-      <c r="H12" s="37" t="n">
-        <v>46310</v>
+      <c r="A12" s="30">
+        <f>INDEX('Risk Register'!$A$2:$A$21,MATCH(ROWS($A$12:A12),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="B12" s="30">
+        <f>INDEX('Risk Register'!$B$2:$B$21,MATCH(ROWS($A$12:A12),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="C12" s="30">
+        <f>INDEX('Risk Register'!$C$2:$C$21,MATCH(ROWS($A$12:A12),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="D12" s="30">
+        <f>INDEX('Risk Register'!$O$2:$O$21,MATCH(ROWS($A$12:A12),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="E12" s="30">
+        <f>INDEX('Risk Register'!$P$2:$P$21,MATCH(ROWS($A$12:A12),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="F12" s="30">
+        <f>INDEX('Risk Register'!$Q$2:$Q$21,MATCH(ROWS($A$12:A12),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="G12" s="30">
+        <f>INDEX('Risk Register'!$S$2:$S$21,MATCH(ROWS($A$12:A12),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="H12" s="37">
+        <f>INDEX('Risk Register'!$T$2:$T$21,MATCH(ROWS($A$12:A12),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>R-002</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>Business Continuity</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>Production SaaS Platform</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="E13" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F13" s="31" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="G13" s="31" t="inlineStr">
-        <is>
-          <t>Director of Infrastructure</t>
-        </is>
-      </c>
-      <c r="H13" s="38" t="n">
-        <v>46356</v>
+      <c r="A13" s="31">
+        <f>INDEX('Risk Register'!$A$2:$A$21,MATCH(ROWS($A$12:A13),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="B13" s="31">
+        <f>INDEX('Risk Register'!$B$2:$B$21,MATCH(ROWS($A$12:A13),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="C13" s="31">
+        <f>INDEX('Risk Register'!$C$2:$C$21,MATCH(ROWS($A$12:A13),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="D13" s="31">
+        <f>INDEX('Risk Register'!$O$2:$O$21,MATCH(ROWS($A$12:A13),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="E13" s="31">
+        <f>INDEX('Risk Register'!$P$2:$P$21,MATCH(ROWS($A$12:A13),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="F13" s="31">
+        <f>INDEX('Risk Register'!$Q$2:$Q$21,MATCH(ROWS($A$12:A13),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="G13" s="31">
+        <f>INDEX('Risk Register'!$S$2:$S$21,MATCH(ROWS($A$12:A13),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="H13" s="38">
+        <f>INDEX('Risk Register'!$T$2:$T$21,MATCH(ROWS($A$12:A13),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>R-003</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>Cloud Security</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>AWS S3 / IAM / Network Configurations</t>
-        </is>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="E14" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F14" s="31" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="G14" s="31" t="inlineStr">
-        <is>
-          <t>Cloud Engineering Manager</t>
-        </is>
-      </c>
-      <c r="H14" s="38" t="n">
-        <v>46326</v>
+      <c r="A14" s="31">
+        <f>INDEX('Risk Register'!$A$2:$A$21,MATCH(ROWS($A$12:A14),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="B14" s="31">
+        <f>INDEX('Risk Register'!$B$2:$B$21,MATCH(ROWS($A$12:A14),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="C14" s="31">
+        <f>INDEX('Risk Register'!$C$2:$C$21,MATCH(ROWS($A$12:A14),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="D14" s="31">
+        <f>INDEX('Risk Register'!$O$2:$O$21,MATCH(ROWS($A$12:A14),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="E14" s="31">
+        <f>INDEX('Risk Register'!$P$2:$P$21,MATCH(ROWS($A$12:A14),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="F14" s="31">
+        <f>INDEX('Risk Register'!$Q$2:$Q$21,MATCH(ROWS($A$12:A14),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="G14" s="31">
+        <f>INDEX('Risk Register'!$S$2:$S$21,MATCH(ROWS($A$12:A14),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="H14" s="38">
+        <f>INDEX('Risk Register'!$T$2:$T$21,MATCH(ROWS($A$12:A14),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>R-007</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>Third-Party Risk</t>
-        </is>
-      </c>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>Customer Data Processors</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F15" s="31" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="G15" s="31" t="inlineStr">
-        <is>
-          <t>GRC Lead</t>
-        </is>
-      </c>
-      <c r="H15" s="38" t="n">
-        <v>46387</v>
+      <c r="A15" s="31">
+        <f>INDEX('Risk Register'!$A$2:$A$21,MATCH(ROWS($A$12:A15),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="B15" s="31">
+        <f>INDEX('Risk Register'!$B$2:$B$21,MATCH(ROWS($A$12:A15),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="C15" s="31">
+        <f>INDEX('Risk Register'!$C$2:$C$21,MATCH(ROWS($A$12:A15),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="D15" s="31">
+        <f>INDEX('Risk Register'!$O$2:$O$21,MATCH(ROWS($A$12:A15),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="E15" s="31">
+        <f>INDEX('Risk Register'!$P$2:$P$21,MATCH(ROWS($A$12:A15),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="F15" s="31">
+        <f>INDEX('Risk Register'!$Q$2:$Q$21,MATCH(ROWS($A$12:A15),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="G15" s="31">
+        <f>INDEX('Risk Register'!$S$2:$S$21,MATCH(ROWS($A$12:A15),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="H15" s="38">
+        <f>INDEX('Risk Register'!$T$2:$T$21,MATCH(ROWS($A$12:A15),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>R-015</t>
-        </is>
-      </c>
-      <c r="B16" s="32" t="inlineStr">
-        <is>
-          <t>Incident Response</t>
-        </is>
-      </c>
-      <c r="C16" s="32" t="inlineStr">
-        <is>
-          <t>Enterprise Incident Process</t>
-        </is>
-      </c>
-      <c r="D16" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F16" s="32" t="inlineStr">
-        <is>
-          <t>Mitigate</t>
-        </is>
-      </c>
-      <c r="G16" s="32" t="inlineStr">
-        <is>
-          <t>CISO</t>
-        </is>
-      </c>
-      <c r="H16" s="39" t="n">
-        <v>46341</v>
+      <c r="A16" s="32">
+        <f>INDEX('Risk Register'!$A$2:$A$21,MATCH(ROWS($A$12:A16),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="B16" s="32">
+        <f>INDEX('Risk Register'!$B$2:$B$21,MATCH(ROWS($A$12:A16),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="C16" s="32">
+        <f>INDEX('Risk Register'!$C$2:$C$21,MATCH(ROWS($A$12:A16),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>INDEX('Risk Register'!$O$2:$O$21,MATCH(ROWS($A$12:A16),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>INDEX('Risk Register'!$P$2:$P$21,MATCH(ROWS($A$12:A16),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>INDEX('Risk Register'!$Q$2:$Q$21,MATCH(ROWS($A$12:A16),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>INDEX('Risk Register'!$S$2:$S$21,MATCH(ROWS($A$12:A16),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
+      </c>
+      <c r="H16" s="39">
+        <f>INDEX('Risk Register'!$T$2:$T$21,MATCH(ROWS($A$12:A16),'Risk Register'!$Y$2:$Y$21,0))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1541,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1568,6 +1548,7 @@
     <col width="22" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1691,6 +1672,11 @@
           <t>CIS / Other Ref</t>
         </is>
       </c>
+      <c r="Y1" s="28" t="inlineStr">
+        <is>
+          <t>Display Rank</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
@@ -1799,6 +1785,10 @@
           <t>CIS 6, CIS 5</t>
         </is>
       </c>
+      <c r="Y2" s="30">
+        <f>RANK(O2,$O$2:$O$21,0)+COUNTIF($O$2:O2,O2)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="31" t="inlineStr">
@@ -1907,6 +1897,10 @@
           <t>CIS 11, CIS 17</t>
         </is>
       </c>
+      <c r="Y3" s="31">
+        <f>RANK(O3,$O$2:$O$21,0)+COUNTIF($O$2:O3,O3)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2015,6 +2009,10 @@
           <t>CIS 4, CIS 12</t>
         </is>
       </c>
+      <c r="Y4" s="31">
+        <f>RANK(O4,$O$2:$O$21,0)+COUNTIF($O$2:O4,O4)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
@@ -2123,8 +2121,12 @@
           <t>CIS 5, CIS 6</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="Y5" s="31">
+        <f>RANK(O5,$O$2:$O$21,0)+COUNTIF($O$2:O5,O5)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="95" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
         <is>
           <t>R-005</t>
@@ -2147,12 +2149,12 @@
       </c>
       <c r="E6" s="31" t="inlineStr">
         <is>
-          <t>Offboarding evidence is not centrally retained</t>
+          <t>Deprovisioning depends on timely HR termination notification; residual risk remains if that upstream trigger is delayed.</t>
         </is>
       </c>
       <c r="F6" s="31" t="inlineStr">
         <is>
-          <t>Terminated users may retain access because account removal evidence is incomplete across connected SaaS systems.</t>
+          <t>A delayed HR termination notification could leave a former employee with access before the otherwise operating removal workflow is triggered.</t>
         </is>
       </c>
       <c r="G6" s="31" t="n">
@@ -2171,12 +2173,12 @@
       </c>
       <c r="K6" s="31" t="inlineStr">
         <is>
-          <t>HR ticketing, SSO deactivation</t>
+          <t>Fictional scenario assumption: SSO deactivation and retained termination records operate consistently when HR notification is received.</t>
         </is>
       </c>
       <c r="L6" s="31" t="inlineStr">
         <is>
-          <t>Partially Effective</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="M6" s="31" t="n">
@@ -2200,7 +2202,7 @@
       </c>
       <c r="R6" s="31" t="inlineStr">
         <is>
-          <t>Automate deprovisioning checklist; sample monthly terminations; retain evidence.</t>
+          <t>Maintain automated deprovisioning and monthly termination sampling; monitor timeliness of HR notification.</t>
         </is>
       </c>
       <c r="S6" s="31" t="inlineStr">
@@ -2231,6 +2233,10 @@
           <t>CIS 5</t>
         </is>
       </c>
+      <c r="Y6" s="31">
+        <f>RANK(O6,$O$2:$O$21,0)+COUNTIF($O$2:O6,O6)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
@@ -2339,6 +2345,10 @@
           <t>CIS 15</t>
         </is>
       </c>
+      <c r="Y7" s="31">
+        <f>RANK(O7,$O$2:$O$21,0)+COUNTIF($O$2:O7,O7)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
@@ -2447,6 +2457,10 @@
           <t>CIS 15</t>
         </is>
       </c>
+      <c r="Y8" s="31">
+        <f>RANK(O8,$O$2:$O$21,0)+COUNTIF($O$2:O8,O8)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -2555,6 +2569,10 @@
           <t>CIS 11</t>
         </is>
       </c>
+      <c r="Y9" s="31">
+        <f>RANK(O9,$O$2:$O$21,0)+COUNTIF($O$2:O9,O9)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -2663,6 +2681,10 @@
           <t>CIS 7</t>
         </is>
       </c>
+      <c r="Y10" s="31">
+        <f>RANK(O10,$O$2:$O$21,0)+COUNTIF($O$2:O10,O10)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
@@ -2771,6 +2793,10 @@
           <t>CIS 14, CIS 9</t>
         </is>
       </c>
+      <c r="Y11" s="31">
+        <f>RANK(O11,$O$2:$O$21,0)+COUNTIF($O$2:O11,O11)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
@@ -2879,6 +2905,10 @@
           <t>CIS 16</t>
         </is>
       </c>
+      <c r="Y12" s="31">
+        <f>RANK(O12,$O$2:$O$21,0)+COUNTIF($O$2:O12,O12)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
@@ -2987,6 +3017,10 @@
           <t>CIS 8</t>
         </is>
       </c>
+      <c r="Y13" s="31">
+        <f>RANK(O13,$O$2:$O$21,0)+COUNTIF($O$2:O13,O13)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
@@ -3095,6 +3129,10 @@
           <t>CIS 7</t>
         </is>
       </c>
+      <c r="Y14" s="31">
+        <f>RANK(O14,$O$2:$O$21,0)+COUNTIF($O$2:O14,O14)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
@@ -3203,8 +3241,12 @@
           <t>CIS 15</t>
         </is>
       </c>
-    </row>
-    <row r="16">
+      <c r="Y15" s="31">
+        <f>RANK(O15,$O$2:$O$21,0)+COUNTIF($O$2:O15,O15)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="95" customHeight="1">
       <c r="A16" s="31" t="inlineStr">
         <is>
           <t>R-015</t>
@@ -3251,16 +3293,16 @@
       </c>
       <c r="K16" s="31" t="inlineStr">
         <is>
-          <t>IR plan, on-call rotation</t>
+          <t>IR plan and on-call rotation exist, but no current exercise validates coordinated response. No demonstrated reduction credited to these controls for this risk.</t>
         </is>
       </c>
       <c r="L16" s="31" t="inlineStr">
         <is>
-          <t>Partially Effective</t>
+          <t>Ineffective</t>
         </is>
       </c>
       <c r="M16" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N16" s="31" t="n">
         <v>5</v>
@@ -3311,6 +3353,10 @@
           <t>CIS 17</t>
         </is>
       </c>
+      <c r="Y16" s="31">
+        <f>RANK(O16,$O$2:$O$21,0)+COUNTIF($O$2:O16,O16)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
@@ -3419,6 +3465,10 @@
           <t>CIS 3</t>
         </is>
       </c>
+      <c r="Y17" s="31">
+        <f>RANK(O17,$O$2:$O$21,0)+COUNTIF($O$2:O17,O17)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
@@ -3527,8 +3577,12 @@
           <t>CIS 11</t>
         </is>
       </c>
-    </row>
-    <row r="19">
+      <c r="Y18" s="31">
+        <f>RANK(O18,$O$2:$O$21,0)+COUNTIF($O$2:O18,O18)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="95" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
         <is>
           <t>R-018</t>
@@ -3551,12 +3605,12 @@
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>Emergency changes lack consistent post-implementation review</t>
+          <t>An unauthorized change can still bypass the normal approval path; retrospective review is a detective control.</t>
         </is>
       </c>
       <c r="F19" s="31" t="inlineStr">
         <is>
-          <t>Production instability or security exposure may occur because emergency changes are not consistently reviewed after implementation.</t>
+          <t>An unauthorized production change could cause exposure before review detects it, despite consistently operating approvals and emergency post-review.</t>
         </is>
       </c>
       <c r="G19" s="31" t="n">
@@ -3575,12 +3629,12 @@
       </c>
       <c r="K19" s="31" t="inlineStr">
         <is>
-          <t>Pull requests, approvals</t>
+          <t>Fictional scenario assumption: pull-request approvals and emergency reviews within five business days operate consistently.</t>
         </is>
       </c>
       <c r="L19" s="31" t="inlineStr">
         <is>
-          <t>Partially Effective</t>
+          <t>Effective</t>
         </is>
       </c>
       <c r="M19" s="31" t="n">
@@ -3604,7 +3658,7 @@
       </c>
       <c r="R19" s="31" t="inlineStr">
         <is>
-          <t>Require emergency change review within five business days; sample monthly.</t>
+          <t>Maintain production approvals and five-business-day emergency review; sample changes monthly.</t>
         </is>
       </c>
       <c r="S19" s="31" t="inlineStr">
@@ -3635,6 +3689,10 @@
           <t>CIS 4</t>
         </is>
       </c>
+      <c r="Y19" s="31">
+        <f>RANK(O19,$O$2:$O$21,0)+COUNTIF($O$2:O19,O19)-1</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
@@ -3743,8 +3801,12 @@
           <t>CIS 14</t>
         </is>
       </c>
-    </row>
-    <row r="21">
+      <c r="Y20" s="31">
+        <f>RANK(O20,$O$2:$O$21,0)+COUNTIF($O$2:O20,O20)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="95" customHeight="1">
       <c r="A21" s="32" t="inlineStr">
         <is>
           <t>R-020</t>
@@ -3791,16 +3853,16 @@
       </c>
       <c r="K21" s="32" t="inlineStr">
         <is>
-          <t>Shared folders, ticketing</t>
+          <t>Shared folders and ticketing lack central evidence ownership and review; they do not meet the evidence-governance objective.</t>
         </is>
       </c>
       <c r="L21" s="32" t="inlineStr">
         <is>
-          <t>Partially Effective</t>
+          <t>Ineffective</t>
         </is>
       </c>
       <c r="M21" s="32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N21" s="32" t="n">
         <v>4</v>
@@ -3850,6 +3912,10 @@
         <is>
           <t>SOC 2 CC2, CC3, CC5</t>
         </is>
+      </c>
+      <c r="Y21" s="32">
+        <f>RANK(O21,$O$2:$O$21,0)+COUNTIF($O$2:O21,O21)-1</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3937,10 +4003,9 @@
           <t>R-001</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B2" s="30">
+        <f>'Risk Register'!P2</f>
+        <v/>
       </c>
       <c r="C2" s="30" t="inlineStr">
         <is>
@@ -3960,10 +4025,9 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G2" s="30" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G2" s="30">
+        <f>B2</f>
+        <v/>
       </c>
       <c r="H2" s="30" t="inlineStr">
         <is>
@@ -3977,10 +4041,9 @@
           <t>R-002</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B3" s="31">
+        <f>'Risk Register'!P3</f>
+        <v/>
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
@@ -4000,10 +4063,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G3" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G3" s="31">
+        <f>B3</f>
+        <v/>
       </c>
       <c r="H3" s="31" t="inlineStr">
         <is>
@@ -4017,10 +4079,9 @@
           <t>R-003</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B4" s="31">
+        <f>'Risk Register'!P4</f>
+        <v/>
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
@@ -4040,10 +4101,9 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G4" s="31">
+        <f>B4</f>
+        <v/>
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
@@ -4057,10 +4117,9 @@
           <t>R-004</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B5" s="31">
+        <f>'Risk Register'!P5</f>
+        <v/>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
@@ -4080,10 +4139,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G5" s="31">
+        <f>B5</f>
+        <v/>
       </c>
       <c r="H5" s="31" t="inlineStr">
         <is>
@@ -4097,14 +4155,13 @@
           <t>R-005</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="B6" s="31">
+        <f>'Risk Register'!P6</f>
+        <v/>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>Automate deprovisioning checklist; sample monthly terminations; retain evidence.</t>
+          <t>Maintain automated deprovisioning and monthly termination sampling; monitor timeliness of HR notification.</t>
         </is>
       </c>
       <c r="D6" s="31" t="inlineStr">
@@ -4120,10 +4177,9 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="G6" s="31">
+        <f>B6</f>
+        <v/>
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
@@ -4137,10 +4193,9 @@
           <t>R-006</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="B7" s="31">
+        <f>'Risk Register'!P7</f>
+        <v/>
       </c>
       <c r="C7" s="31" t="inlineStr">
         <is>
@@ -4160,10 +4215,9 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="G7" s="31">
+        <f>B7</f>
+        <v/>
       </c>
       <c r="H7" s="31" t="inlineStr">
         <is>
@@ -4177,10 +4231,9 @@
           <t>R-007</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B8" s="31">
+        <f>'Risk Register'!P8</f>
+        <v/>
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
@@ -4200,10 +4253,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G8" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G8" s="31">
+        <f>B8</f>
+        <v/>
       </c>
       <c r="H8" s="31" t="inlineStr">
         <is>
@@ -4217,10 +4269,9 @@
           <t>R-008</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B9" s="31">
+        <f>'Risk Register'!P9</f>
+        <v/>
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
@@ -4240,10 +4291,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G9" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G9" s="31">
+        <f>B9</f>
+        <v/>
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
@@ -4257,10 +4307,9 @@
           <t>R-009</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B10" s="31">
+        <f>'Risk Register'!P10</f>
+        <v/>
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
@@ -4280,10 +4329,9 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G10" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G10" s="31">
+        <f>B10</f>
+        <v/>
       </c>
       <c r="H10" s="31" t="inlineStr">
         <is>
@@ -4297,10 +4345,9 @@
           <t>R-010</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B11" s="31">
+        <f>'Risk Register'!P11</f>
+        <v/>
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
@@ -4320,10 +4367,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G11" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G11" s="31">
+        <f>B11</f>
+        <v/>
       </c>
       <c r="H11" s="31" t="inlineStr">
         <is>
@@ -4337,10 +4383,9 @@
           <t>R-011</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B12" s="31">
+        <f>'Risk Register'!P12</f>
+        <v/>
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
@@ -4360,10 +4405,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G12" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G12" s="31">
+        <f>B12</f>
+        <v/>
       </c>
       <c r="H12" s="31" t="inlineStr">
         <is>
@@ -4377,10 +4421,9 @@
           <t>R-012</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B13" s="31">
+        <f>'Risk Register'!P13</f>
+        <v/>
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
@@ -4400,10 +4443,9 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G13" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G13" s="31">
+        <f>B13</f>
+        <v/>
       </c>
       <c r="H13" s="31" t="inlineStr">
         <is>
@@ -4417,10 +4459,9 @@
           <t>R-013</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B14" s="31">
+        <f>'Risk Register'!P14</f>
+        <v/>
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
@@ -4440,10 +4481,9 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G14" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G14" s="31">
+        <f>B14</f>
+        <v/>
       </c>
       <c r="H14" s="31" t="inlineStr">
         <is>
@@ -4457,10 +4497,9 @@
           <t>R-014</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="B15" s="31">
+        <f>'Risk Register'!P15</f>
+        <v/>
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
@@ -4480,10 +4519,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G15" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="G15" s="31">
+        <f>B15</f>
+        <v/>
       </c>
       <c r="H15" s="31" t="inlineStr">
         <is>
@@ -4497,10 +4535,9 @@
           <t>R-015</t>
         </is>
       </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B16" s="31">
+        <f>'Risk Register'!P16</f>
+        <v/>
       </c>
       <c r="C16" s="31" t="inlineStr">
         <is>
@@ -4520,14 +4557,13 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G16" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G16" s="31">
+        <f>B16</f>
+        <v/>
       </c>
       <c r="H16" s="31" t="inlineStr">
         <is>
-          <t>Track in monthly GRC remediation review</t>
+          <t>Critical residual 20. Escalate to leadership; tabletop and corrective-action evidence required before crediting risk reduction.</t>
         </is>
       </c>
     </row>
@@ -4537,10 +4573,9 @@
           <t>R-016</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="B17" s="31">
+        <f>'Risk Register'!P17</f>
+        <v/>
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
@@ -4560,10 +4595,9 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G17" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="G17" s="31">
+        <f>B17</f>
+        <v/>
       </c>
       <c r="H17" s="31" t="inlineStr">
         <is>
@@ -4577,10 +4611,9 @@
           <t>R-017</t>
         </is>
       </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B18" s="31">
+        <f>'Risk Register'!P18</f>
+        <v/>
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
@@ -4600,10 +4633,9 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G18" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G18" s="31">
+        <f>B18</f>
+        <v/>
       </c>
       <c r="H18" s="31" t="inlineStr">
         <is>
@@ -4617,14 +4649,13 @@
           <t>R-018</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="B19" s="31">
+        <f>'Risk Register'!P19</f>
+        <v/>
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>Require emergency change review within five business days; sample monthly.</t>
+          <t>Maintain production approvals and five-business-day emergency review; sample changes monthly.</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
@@ -4640,10 +4671,9 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G19" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="G19" s="31">
+        <f>B19</f>
+        <v/>
       </c>
       <c r="H19" s="31" t="inlineStr">
         <is>
@@ -4657,10 +4687,9 @@
           <t>R-019</t>
         </is>
       </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="B20" s="31">
+        <f>'Risk Register'!P20</f>
+        <v/>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
@@ -4680,10 +4709,9 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G20" s="31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+      <c r="G20" s="31">
+        <f>B20</f>
+        <v/>
       </c>
       <c r="H20" s="31" t="inlineStr">
         <is>
@@ -4697,10 +4725,9 @@
           <t>R-020</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B21" s="32">
+        <f>'Risk Register'!P21</f>
+        <v/>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
@@ -4720,14 +4747,13 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="G21" s="32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="G21" s="32">
+        <f>B21</f>
+        <v/>
       </c>
       <c r="H21" s="32" t="inlineStr">
         <is>
-          <t>Track in monthly GRC remediation review</t>
+          <t>Residual 16 equals inherent: existing storage tools do not constitute an effective evidence-governance process.</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5069,6 +5095,23 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>Scenario dates and rating definitions</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>Fictional assessment assumptions; see shared company profile</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>../../00-company-profile/Northbridge-Company-and-GRC-Scope.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
